--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F617B188-897E-4DE4-85DE-E5680707CBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C90085-2F80-4528-B89C-30A3315F72B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
+    <workbookView xWindow="1305" yWindow="2835" windowWidth="21600" windowHeight="11295" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025-2026" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -127,7 +127,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -516,7 +516,9 @@
       <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -570,7 +572,9 @@
       <c r="G5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -666,7 +670,9 @@
       <c r="G9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C90085-2F80-4528-B89C-30A3315F72B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014C294D-CF19-4BE2-900B-C69DCF476D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="2835" windowWidth="21600" windowHeight="11295" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
+    <workbookView xWindow="14715" yWindow="330" windowWidth="13785" windowHeight="14175" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025-2026" sheetId="1" r:id="rId1"/>
@@ -470,6 +470,9 @@
       <c r="H1" s="1">
         <v>46087</v>
       </c>
+      <c r="I1" s="1">
+        <v>46093</v>
+      </c>
     </row>
     <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014C294D-CF19-4BE2-900B-C69DCF476D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB20D0F4-52FA-4A68-A846-14E357C24C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14715" yWindow="330" windowWidth="13785" windowHeight="14175" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -493,7 +493,9 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
@@ -522,7 +524,9 @@
       <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -578,7 +582,9 @@
       <c r="H5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB20D0F4-52FA-4A68-A846-14E357C24C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80956098-0B20-4304-9364-B63B26D12AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14715" yWindow="330" windowWidth="13785" windowHeight="14175" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025-2026" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,12 +90,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -112,7 +118,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -123,6 +129,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -439,13 +448,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C439B3A-2AB9-40EE-9E30-5B19DA870949}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="10" width="10.625" customWidth="1"/>
+    <col min="2" max="11" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -473,8 +482,14 @@
       <c r="I1" s="1">
         <v>46093</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J1" s="1">
+        <v>46096</v>
+      </c>
+      <c r="K1" s="1">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -497,11 +512,14 @@
         <v>9</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="K2" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-    </row>
-    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -531,8 +549,9 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -556,8 +575,9 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -589,8 +609,9 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -614,8 +635,9 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -631,12 +653,15 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="J7" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -660,8 +685,9 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -687,8 +713,9 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -700,7 +727,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:H9 I2:M9" xr:uid="{55CC9427-6E71-48F6-BB9B-DD6B42E4148B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:H9 I2:N9" xr:uid="{55CC9427-6E71-48F6-BB9B-DD6B42E4148B}">
       <formula1>"√,×"</formula1>
     </dataValidation>
   </dataValidations>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80956098-0B20-4304-9364-B63B26D12AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496B45CE-01A3-4386-ACB0-3BE76076BE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -452,6 +452,7 @@
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -487,6 +488,9 @@
       </c>
       <c r="K1" s="1">
         <v>46097</v>
+      </c>
+      <c r="L1" s="1">
+        <v>46100</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -607,7 +611,9 @@
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="L5" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
@@ -633,7 +639,9 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496B45CE-01A3-4386-ACB0-3BE76076BE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D07A40-3033-45CF-A087-63FB81A02A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -452,7 +452,7 @@
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -491,6 +491,9 @@
       </c>
       <c r="L1" s="1">
         <v>46100</v>
+      </c>
+      <c r="M1" s="1">
+        <v>46102</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -578,7 +581,6 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -614,7 +616,9 @@
       <c r="L5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="3"/>
+      <c r="M5" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -692,7 +696,9 @@
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="M8" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -735,7 +741,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:H9 I2:N9" xr:uid="{55CC9427-6E71-48F6-BB9B-DD6B42E4148B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:N9" xr:uid="{55CC9427-6E71-48F6-BB9B-DD6B42E4148B}">
       <formula1>"√,×"</formula1>
     </dataValidation>
   </dataValidations>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D07A40-3033-45CF-A087-63FB81A02A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B5EBC1-2C47-4E1E-A988-0CF00CA86EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -452,7 +452,7 @@
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="13" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -495,6 +495,9 @@
       <c r="M1" s="1">
         <v>46102</v>
       </c>
+      <c r="N1" s="1">
+        <v>46108</v>
+      </c>
     </row>
     <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -524,7 +527,9 @@
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="N2" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -556,7 +561,9 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
+      <c r="N3" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -581,7 +588,9 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="N4" s="3"/>
+      <c r="N4" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -619,7 +628,9 @@
       <c r="M5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="3"/>
+      <c r="N5" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -647,7 +658,9 @@
         <v>9</v>
       </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
+      <c r="N6" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -671,7 +684,9 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
+      <c r="N7" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -699,7 +714,9 @@
       <c r="M8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="3"/>
+      <c r="N8" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -727,7 +744,9 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
+      <c r="N9" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B5EBC1-2C47-4E1E-A988-0CF00CA86EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CCCD78B-AB3F-428E-BACB-C187F2EC849C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,14 +448,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C439B3A-2AB9-40EE-9E30-5B19DA870949}">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="11" width="10.625" customWidth="1"/>
     <col min="12" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -498,8 +499,14 @@
       <c r="N1" s="1">
         <v>46108</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O1" s="1">
+        <v>46119</v>
+      </c>
+      <c r="P1" s="1">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -530,8 +537,9 @@
       <c r="N2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -564,8 +572,9 @@
       <c r="N3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -591,8 +600,9 @@
       <c r="N4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -631,8 +641,9 @@
       <c r="N5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -661,8 +672,11 @@
       <c r="N6" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -687,8 +701,9 @@
       <c r="N7" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -717,8 +732,12 @@
       <c r="N8" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+      <c r="P8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -747,8 +766,11 @@
       <c r="N9" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -760,7 +782,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:N9" xr:uid="{55CC9427-6E71-48F6-BB9B-DD6B42E4148B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:O9 P1:T9" xr:uid="{55CC9427-6E71-48F6-BB9B-DD6B42E4148B}">
       <formula1>"√,×"</formula1>
     </dataValidation>
   </dataValidations>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CCCD78B-AB3F-428E-BACB-C187F2EC849C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CDF263-6F18-4EF9-BF39-00E6E7DF20E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,15 +448,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C439B3A-2AB9-40EE-9E30-5B19DA870949}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="11" width="10.625" customWidth="1"/>
     <col min="12" max="14" width="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -505,8 +506,11 @@
       <c r="P1" s="1">
         <v>46120</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q1" s="1">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -539,7 +543,7 @@
       </c>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -574,7 +578,7 @@
       </c>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -602,7 +606,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -643,7 +647,7 @@
       </c>
       <c r="O5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -675,8 +679,11 @@
       <c r="O6" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -703,7 +710,7 @@
       </c>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -736,8 +743,11 @@
       <c r="P8" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Q8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -770,7 +780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -781,11 +791,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:O9 P1:T9" xr:uid="{55CC9427-6E71-48F6-BB9B-DD6B42E4148B}">
-      <formula1>"√,×"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CDF263-6F18-4EF9-BF39-00E6E7DF20E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11653E0B-2045-4A0D-B167-D86D02E3A83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,16 +448,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C439B3A-2AB9-40EE-9E30-5B19DA870949}">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="11" width="10.625" customWidth="1"/>
     <col min="12" max="14" width="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -509,8 +509,11 @@
       <c r="Q1" s="1">
         <v>46122</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R1" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -543,7 +546,7 @@
       </c>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -578,7 +581,7 @@
       </c>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -606,7 +609,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -646,8 +649,11 @@
         <v>9</v>
       </c>
       <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -683,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -710,7 +716,7 @@
       </c>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -747,7 +753,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -779,8 +785,11 @@
       <c r="O9" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11653E0B-2045-4A0D-B167-D86D02E3A83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683AEA3C-A2A3-40B6-9706-EC4FF6179E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,16 +448,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C439B3A-2AB9-40EE-9E30-5B19DA870949}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="11" width="10.625" customWidth="1"/>
     <col min="12" max="14" width="10" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="17" max="18" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -512,8 +512,11 @@
       <c r="R1" s="1">
         <v>46125</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S1" s="1">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -546,7 +549,7 @@
       </c>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -581,7 +584,7 @@
       </c>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -609,7 +612,7 @@
       </c>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -652,8 +655,11 @@
       <c r="R5" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -688,8 +694,11 @@
       <c r="Q6" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -716,7 +725,7 @@
       </c>
       <c r="O7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -753,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -789,7 +798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11653E0B-2045-4A0D-B167-D86D02E3A83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63AF319-3D2F-4700-8B27-1ED6261D29EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="10">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,7 +73,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +84,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
@@ -118,7 +126,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -133,6 +141,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,16 +459,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C439B3A-2AB9-40EE-9E30-5B19DA870949}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="17" max="18" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="10" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -512,8 +530,23 @@
       <c r="R1" s="1">
         <v>46125</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S1" s="1">
+        <v>46127</v>
+      </c>
+      <c r="T1" s="1">
+        <v>46132</v>
+      </c>
+      <c r="U1" s="1">
+        <v>46133</v>
+      </c>
+      <c r="V1" s="1">
+        <v>46134</v>
+      </c>
+      <c r="W1" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -545,8 +578,14 @@
         <v>9</v>
       </c>
       <c r="O2" s="3"/>
-    </row>
-    <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="V2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -580,9 +619,12 @@
         <v>9</v>
       </c>
       <c r="O3" s="3"/>
-    </row>
-    <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="V3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -608,8 +650,11 @@
         <v>9</v>
       </c>
       <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="V4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -652,8 +697,14 @@
       <c r="R5" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -688,9 +739,18 @@
       <c r="Q6" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="S6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -715,8 +775,11 @@
         <v>9</v>
       </c>
       <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -752,8 +815,14 @@
       <c r="Q8" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -789,7 +858,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63AF319-3D2F-4700-8B27-1ED6261D29EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44222E03-9E30-4D09-B49A-84CB685658E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2025-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025-2026'!$B$2:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025-2026'!$C$2:$I$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="14">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,6 +67,22 @@
   </si>
   <si>
     <t>√</t>
+  </si>
+  <si>
+    <t>论文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>U 档案材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手写封面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -142,8 +158,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,101 +475,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C439B3A-2AB9-40EE-9E30-5B19DA870949}">
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="24" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1">
         <v>45995</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>46006</v>
-      </c>
-      <c r="D1" s="1">
-        <v>46029</v>
       </c>
       <c r="E1" s="1">
         <v>46029</v>
       </c>
       <c r="F1" s="1">
+        <v>46029</v>
+      </c>
+      <c r="G1" s="1">
         <v>46038</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>46041</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>46087</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>46093</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>46096</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>46097</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>46100</v>
       </c>
-      <c r="M1" s="1">
+      <c r="N1" s="1">
         <v>46102</v>
       </c>
-      <c r="N1" s="1">
+      <c r="O1" s="1">
         <v>46108</v>
       </c>
-      <c r="O1" s="1">
+      <c r="P1" s="1">
         <v>46119</v>
       </c>
-      <c r="P1" s="1">
+      <c r="Q1" s="1">
         <v>46120</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="R1" s="1">
         <v>46122</v>
       </c>
-      <c r="R1" s="1">
+      <c r="S1" s="1">
         <v>46125</v>
       </c>
-      <c r="S1" s="1">
+      <c r="T1" s="1">
         <v>46127</v>
       </c>
-      <c r="T1" s="1">
+      <c r="U1" s="1">
         <v>46132</v>
       </c>
-      <c r="U1" s="1">
+      <c r="V1" s="1">
         <v>46133</v>
       </c>
-      <c r="V1" s="1">
+      <c r="W1" s="1">
         <v>46134</v>
       </c>
-      <c r="W1" s="1">
+      <c r="X1" s="1">
         <v>46141</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -562,37 +573,40 @@
       <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3"/>
+      <c r="L2" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="M2" s="3"/>
-      <c r="N2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="3"/>
-      <c r="V2" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="3"/>
       <c r="W2" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="X2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -601,36 +615,36 @@
       <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="3"/>
-      <c r="V3" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N3" s="3"/>
+      <c r="O3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="3"/>
+      <c r="W3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -639,29 +653,29 @@
       <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="N4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="3"/>
-      <c r="V4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="M4" s="3"/>
+      <c r="O4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="W4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -682,36 +696,36 @@
       <c r="I5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="3"/>
+      <c r="J5" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="K5" s="3"/>
-      <c r="L5" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="L5" s="3"/>
       <c r="M5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O5" s="3"/>
-      <c r="R5" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="N5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P5" s="3"/>
       <c r="S5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="V5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="T5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -720,152 +734,158 @@
       <c r="E6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="4" t="s">
+      <c r="L6" s="3"/>
+      <c r="M6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="R6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="T6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="V6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3"/>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="3"/>
-      <c r="U7" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="N7" s="3"/>
+      <c r="O7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="3"/>
+      <c r="V7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="M8" s="3"/>
+      <c r="N8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="3"/>
       <c r="Q8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="R8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44222E03-9E30-4D09-B49A-84CB685658E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166CA900-0066-47F3-919A-B3ADB24C1DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="13">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,10 +78,6 @@
   </si>
   <si>
     <t>U 档案材料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手写封面</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -562,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
@@ -675,6 +671,9 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
@@ -724,6 +723,9 @@
     <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166CA900-0066-47F3-919A-B3ADB24C1DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65629650-9D3A-4418-873A-6779258B3A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="work" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025-2026'!$C$2:$I$9</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="37">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,6 +80,99 @@
   <si>
     <t>U 档案材料</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-2026-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025-2026-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-2027-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>课程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>课时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机网络</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机应用基础</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件项目管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23计算机12班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25机械1-2班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25机械3-4班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25机械7-8班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25计科4班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25计科6班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24计科4班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24计科2班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24计科6班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汇总</t>
+  </si>
+  <si>
+    <t>实际课时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结课</t>
+  </si>
+  <si>
+    <t>授课</t>
   </si>
 </sst>
 </file>
@@ -172,6 +266,27 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A322A64-28FB-4665-8D43-A0E4C71D1C96}" name="表1" displayName="表1" ref="A1:F11" totalsRowCount="1">
+  <autoFilter ref="A1:F10" xr:uid="{1A322A64-28FB-4665-8D43-A0E4C71D1C96}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="结课"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{C5254627-FA8A-4E01-A198-1D51028D2712}" name="学期" totalsRowLabel="汇总"/>
+    <tableColumn id="2" xr3:uid="{57E33647-4F73-4731-92CC-501FB9F9F102}" name="课程" totalsRowFunction="count"/>
+    <tableColumn id="4" xr3:uid="{55786C4F-B596-4E79-8CEC-DB485EC8E79C}" name="班级" totalsRowFunction="count"/>
+    <tableColumn id="3" xr3:uid="{35E11D61-DF1D-4423-8286-8527F3F6C5A0}" name="课时" totalsRowFunction="sum"/>
+    <tableColumn id="5" xr3:uid="{B71B17B5-CAFE-4A1E-918C-A997E94C4078}" name="实际课时" totalsRowFunction="sum"/>
+    <tableColumn id="6" xr3:uid="{EE7624EE-31BE-4909-BF8A-3B99C721EE22}" name="状态"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -893,4 +1008,250 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2F3060-25CF-41B6-84B9-85ACF745730F}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>48</v>
+      </c>
+      <c r="E2">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>48</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4">
+        <v>48</v>
+      </c>
+      <c r="E4">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>48</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10">
+        <v>48</v>
+      </c>
+      <c r="E10">
+        <v>48</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11">
+        <f>SUBTOTAL(103,表1[课程])</f>
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <f>SUBTOTAL(103,表1[班级])</f>
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <f>SUBTOTAL(109,表1[课时])</f>
+        <v>272</v>
+      </c>
+      <c r="E11">
+        <f>SUBTOTAL(109,表1[实际课时])</f>
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F10" xr:uid="{43BD438B-3863-4334-B39F-4DF155038E7A}">
+      <formula1>"结课,授课"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65629650-9D3A-4418-873A-6779258B3A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025-2026" sheetId="1" r:id="rId1"/>

--- a/utils/file/paper.xlsx
+++ b/utils/file/paper.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\utils\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65629650-9D3A-4418-873A-6779258B3A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082213DB-3E9B-4062-9837-C6D06EBA60F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{BFD98EF5-1B00-4EFB-A1F5-EAEBE96890F2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025-2026" sheetId="1" r:id="rId1"/>
     <sheet name="work" sheetId="2" r:id="rId2"/>
+    <sheet name="2026-2027-1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2025-2026'!$C$2:$I$9</definedName>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="49">
   <si>
     <t>张文越</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,6 +174,54 @@
   </si>
   <si>
     <t>授课</t>
+  </si>
+  <si>
+    <t>10-601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机应用基础补考</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江国裕、冯伟昌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transactor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单晴敏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Event</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Location</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13:30-15:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1254,4 +1303,67 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2A24A8-D633-44C1-BBF9-DEBEEE85AC8B}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>